--- a/templates/xlsx/hook-library.xlsx
+++ b/templates/xlsx/hook-library.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hook Library" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>

--- a/templates/xlsx/hook-library.xlsx
+++ b/templates/xlsx/hook-library.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Hook (first 0-3s)</t>
+          <t>Hook (beat A 0-3s; must hold viewers through second 6)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>3s retention %</t>
+          <t>6s retention % (CC: ~60 of 100 → pushed to next pool)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -1155,13 +1155,13 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D2:D201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Relatable,Pain escalation,Curiosity,Visual wow,Context clash,Before/after tease,Myth vs fact"</formula1>
+      <formula1>"Relatable,Pain escalation,Curiosity,Visual wow,Context clash,Before/after tease,Myth vs fact (aiOS addition)"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Demo,Test/experiment,Comparison,Before/after,Credentials,Social proof"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pain-agitate-solve,Review/test,Comparison,Scene,Creator recommendation,Gifting/occasion,Context clash,Visual wow,Day-in-the-life,Unboxing"</formula1>
+      <formula1>"Pain-agitate-solve,Review/test,Comparison,Scene,Creator recommendation,Gifting/occasion,Context clash,Visual wow,Day-in-the-life,Unboxing (aiOS addition)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1190,7 +1190,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Decompose every winning video (ours or reference) into hook / proof / scene / CTA, then recombine. The library is company capability.</t>
+          <t>Decompose every winning video (ours or reference) into hook / proof / scene / CTA, then recombine. The library is company capability. Keep meme/personality one-offs out: CC's rule is that ~99% of selling hits follow the standard framework and ~1% can't be replicated.</t>
         </is>
       </c>
     </row>
